--- a/ClosedXML_Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
+++ b/ClosedXML_Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
@@ -135,7 +135,7 @@
 <x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt" cacheId="0" dataCaption="Values" showError="0" missingCaption="" showMissing="1" pageWrap="0" pageOverThenDown="0" indent="1">
   <x:location ref="A1" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <x:pivotFields count="6">
-    <x:pivotField name="Name" axis="axisCol" defaultSubtotal="0">
+    <x:pivotField name="Name" axis="axisCol" showAll="0" defaultSubtotal="0">
       <x:items count="5">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -147,7 +147,7 @@
     <x:pivotField name="Code" defaultSubtotal="0"/>
     <x:pivotField name="NumberOfOrders" dataField="1" defaultSubtotal="0"/>
     <x:pivotField name="Quality" defaultSubtotal="0"/>
-    <x:pivotField name="Month" axis="axisRow" defaultSubtotal="0"/>
+    <x:pivotField name="Month" axis="axisRow" showAll="0" defaultSubtotal="0"/>
     <x:pivotField name="BakeDate" defaultSubtotal="0"/>
   </x:pivotFields>
   <x:rowFields count="1">

--- a/ClosedXML_Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
+++ b/ClosedXML_Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
@@ -823,7 +823,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:F17" sheet="Pastry Sales Data"/>
   </x:cacheSource>
